--- a/Reports/Module_Analysis_Report.xlsx
+++ b/Reports/Module_Analysis_Report.xlsx
@@ -462,7 +462,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.52</v>
+        <v>78.34</v>
       </c>
       <c r="C2" t="n">
         <v>100</v>
@@ -471,7 +471,7 @@
         <v>6.67</v>
       </c>
       <c r="E2" t="n">
-        <v>18.49</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="3">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71.51000000000001</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="C3" t="n">
         <v>100</v>
@@ -490,7 +490,7 @@
         <v>12.5</v>
       </c>
       <c r="E3" t="n">
-        <v>21.08</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73.03</v>
+        <v>74.69</v>
       </c>
       <c r="C4" t="n">
         <v>95</v>
@@ -509,7 +509,7 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>21.06</v>
+        <v>19.09</v>
       </c>
     </row>
   </sheetData>
